--- a/jpcore-r4b/develop/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medication.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medication.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="281">
   <si>
     <t>Property</t>
   </si>
@@ -631,92 +631,88 @@
     <t>比率（Ratio)を表すデータ型は、量(Quantity)と共通単位を使って適切に表現できないときのみに使われるべきである。分母が"1"に固定されているとわかっているような場合は、量(Quantity)を比率(Ratio)の代わりに使うべきである。</t>
   </si>
   <si>
+    <t>.quantity</t>
+  </si>
+  <si>
+    <t>Medication.ingredient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>薬効がある、あるいは薬効を伴わない成分</t>
+  </si>
+  <si>
+    <t>この薬剤を構成する特定の重要成分を識別する</t>
+  </si>
+  <si>
+    <t>すべての成分を含む必要はない。もし、ある成分が記載されていなくてもその成分が含有されているかどうかを必ずしも意味しない。特定の成分が記載されていても、すべての成分が記載されていると言うことを意味しない。有効成分であるか、有効成分ではないかを指定することは可能である。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
+  </si>
+  <si>
+    <t>.scopesRole[typeCode=INGR]</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.extension:drugNo</t>
+  </si>
+  <si>
+    <t>drugNo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Medication_Ingredient_DrugNo}
+</t>
+  </si>
+  <si>
+    <t>RP内の薬剤の連番</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-rat-1:Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.exists() and denominator.exists()) or (numerator.empty() and denominator.empty() and extension.exists())}</t>
-  </si>
-  <si>
-    <t>RTO</t>
-  </si>
-  <si>
-    <t>Medication.ingredient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>薬効がある、あるいは薬効を伴わない成分</t>
-  </si>
-  <si>
-    <t>この薬剤を構成する特定の重要成分を識別する</t>
-  </si>
-  <si>
-    <t>すべての成分を含む必要はない。もし、ある成分が記載されていなくてもその成分が含有されているかどうかを必ずしも意味しない。特定の成分が記載されていても、すべての成分が記載されていると言うことを意味しない。有効成分であるか、有効成分ではないかを指定することは可能である。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
-  </si>
-  <si>
-    <t>.scopesRole[typeCode=INGR]</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.extension:drugNo</t>
-  </si>
-  <si>
-    <t>drugNo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Medication_Ingredient_DrugNo}
-</t>
-  </si>
-  <si>
-    <t>RP内の薬剤の連番</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -791,6 +787,12 @@
     <t>Ratioデータ型は2つの数字の関係で示され、Quantityや一般的な単位で適切に表現できない関係を表すときにのみ用いられる。分母の値が「1」で固定されているような値であれば、QuantityがRatioの代わりに用いられるべきである。</t>
   </si>
   <si>
+    <t>//element(*,DrugCodedType)/Strength</t>
+  </si>
+  <si>
+    <t>RXC-3-Component Amount &amp; RXC-4-Component Units  if medication: RXO-2-Requested Give Amount - Minimum &amp; RXO-4-Requested Give Units / RXO-3-Requested Give Amount - Maximum &amp; RXO-4-Requested Give Units / RXO-11-Requested Dispense Amount &amp; RXO-12-Requested Dispense Units / RXE-3-Give Amount - Minimum &amp; RXE-5-Give Units / RXE-4-Give Amount - Maximum &amp; RXE-5-Give Units / RXE-10-Dispense Amount &amp; RXE-10-Dispense Units</t>
+  </si>
+  <si>
     <t>Medication.ingredient.strength.id</t>
   </si>
   <si>
@@ -829,23 +831,13 @@
     <t>投与量</t>
   </si>
   <si>
-    <t>薬剤に関する数量と単位を定めたデータイプ</t>
-  </si>
-  <si>
-    <t>薬剤に関する数量と単位を定めている。ValueおよびCodeを必須としている。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
+    <t>The value of the numerator.</t>
   </si>
   <si>
     <t>Ratio.numerator</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>.numerator</t>
   </si>
   <si>
     <t>Medication.ingredient.strength.denominator</t>
@@ -854,7 +846,13 @@
     <t>パッケージ量</t>
   </si>
   <si>
+    <t>The value of the denominator.</t>
+  </si>
+  <si>
     <t>Ratio.denominator</t>
+  </si>
+  <si>
+    <t>.denominator</t>
   </si>
   <si>
     <t>Medication.batch</t>
@@ -1254,7 +1252,7 @@
     <col min="37" max="37" width="195.5390625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.9296875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="173.4375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2994,7 +2992,7 @@
         <v>78</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>189</v>
@@ -3065,30 +3063,30 @@
         <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>195</v>
-      </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3111,16 +3109,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3170,7 +3168,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3182,13 +3180,13 @@
         <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3199,10 +3197,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3225,13 +3223,13 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3282,7 +3280,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3300,7 +3298,7 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3311,10 +3309,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3340,10 +3338,10 @@
         <v>136</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3382,17 +3380,17 @@
         <v>78</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3421,13 +3419,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>78</v>
@@ -3449,13 +3447,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3506,7 +3504,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3515,10 +3513,10 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -3535,14 +3533,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3564,10 +3562,10 @@
         <v>136</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>139</v>
@@ -3622,7 +3620,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3651,10 +3649,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3680,16 +3678,16 @@
         <v>154</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -3738,7 +3736,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>89</v>
@@ -3756,21 +3754,21 @@
         <v>160</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>231</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3793,17 +3791,17 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -3852,7 +3850,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3870,7 +3868,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -3881,10 +3879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3910,13 +3908,13 @@
         <v>189</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3966,7 +3964,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3975,30 +3973,30 @@
         <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="AJ24" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>195</v>
-      </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>133</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4024,10 +4022,10 @@
         <v>91</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4078,7 +4076,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4096,7 +4094,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4107,10 +4105,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4139,7 +4137,7 @@
         <v>137</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>139</v>
@@ -4180,19 +4178,19 @@
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4210,7 +4208,7 @@
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4221,13 +4219,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>78</v>
@@ -4249,13 +4247,13 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4306,7 +4304,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4335,10 +4333,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4358,20 +4356,18 @@
         <v>78</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N28" t="s" s="2">
         <v>255</v>
       </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4429,30 +4425,30 @@
         <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AK28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>258</v>
-      </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4472,20 +4468,18 @@
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -4534,7 +4528,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4543,22 +4537,22 @@
         <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>257</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30">
@@ -4589,7 +4583,7 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>264</v>
@@ -4658,7 +4652,7 @@
         <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>176</v>
@@ -4701,13 +4695,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4758,7 +4752,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -4776,7 +4770,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -4819,7 +4813,7 @@
         <v>137</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>139</v>
@@ -4872,7 +4866,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -4890,7 +4884,7 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -4908,7 +4902,7 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4930,10 +4924,10 @@
         <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>139</v>
@@ -4988,7 +4982,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5043,7 +5037,7 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>271</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medication.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="282">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -374,7 +374,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -784,7 +784,7 @@
     <t>この薬剤中にどの程度の物質が含まれているかを示す。たとえば、1錠あたり250mgなど。これは分子が250mgで分母が1錠である比率を表現している。</t>
   </si>
   <si>
-    <t>Ratioデータ型は2つの数字の関係で示され、Quantityや一般的な単位で適切に表現できない関係を表すときにのみ用いられる。分母の値が「1」で固定されているような値であれば、QuantityがRatioの代わりに用いられるべきである。</t>
+    <t>1回に使用される薬剤量を示すため、denominatorは1回に固定される。</t>
   </si>
   <si>
     <t>//element(*,DrugCodedType)/Strength</t>
@@ -847,6 +847,14 @@
   </si>
   <si>
     <t>The value of the denominator.</t>
+  </si>
+  <si>
+    <t>&lt;valueQuantity xmlns="http://hl7.org/fhir"&gt;
+  &lt;value value="1"/&gt;
+  &lt;unit value="回"/&gt;
+  &lt;system value="http://jpfhir.jp/fhir/core/mhlw/CodeSystem/MedicationUnitMERIT9Code"/&gt;
+  &lt;code value="TIME"/&gt;
+&lt;/valueQuantity&gt;</t>
   </si>
   <si>
     <t>Ratio.denominator</t>
@@ -1214,17 +1222,17 @@
   <dimension ref="A1:AN35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.82421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.73046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.4296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.77734375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.40625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="106.484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="91.2890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1233,25 +1241,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="55.39453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.87890625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="47.4921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.48046875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="195.5390625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="98.9296875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="167.640625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="84.81640625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -4489,7 +4497,7 @@
         <v>78</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>78</v>
@@ -4528,7 +4536,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4546,7 +4554,7 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -4557,10 +4565,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4586,10 +4594,10 @@
         <v>195</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4640,7 +4648,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4658,7 +4666,7 @@
         <v>176</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -4669,10 +4677,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4781,10 +4789,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4895,10 +4903,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5011,10 +5019,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5040,13 +5048,13 @@
         <v>202</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5096,7 +5104,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5120,15 +5128,15 @@
         <v>78</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5151,13 +5159,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5208,7 +5216,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5226,13 +5234,13 @@
         <v>176</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medication.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medication.xlsx
@@ -269,8 +269,8 @@
 このResourceは薬剤を処方し、払い出し（調剤）、その投与を定義し、IDを付与するためにまず利用され、薬剤の使用状態を示すためにも使われる。</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>NewRx/MedicationPrescribed@@ -320,16 +320,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -340,13 +340,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -359,19 +359,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -391,13 +391,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -417,19 +417,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -447,33 +447,34 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Medication.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -542,7 +543,7 @@
     <t>Medication.status</t>
   </si>
   <si>
-    <t>active | inactive | entered-in-error</t>
+    <t>アクティブ|非アクティブ|エラー入力 / active | inactive | entered-in-error</t>
   </si>
   <si>
     <t>薬剤が有効に使われているかどうかを指定するコード。</t>
@@ -554,7 +555,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>A coded concept defining if the medication is in active use.</t>
+    <t>薬が積極的に使用されているかどうかを定義するコード化された概念。 / A coded concept defining if the medication is in active use.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medication-status|4.3.0</t>
@@ -650,7 +651,7 @@
     <t>すべての成分を含む必要はない。もし、ある成分が記載されていなくてもその成分が含有されているかどうかを必ずしも意味しない。特定の成分が記載されていても、すべての成分が記載されていると言うことを意味しない。有効成分であるか、有効成分ではないかを指定することは可能である。</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -664,10 +665,10 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -712,8 +713,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Medication.ingredient.modifierExtension</t>
@@ -723,10 +724,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -799,7 +801,7 @@
     <t>Medication.ingredient.strength.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
@@ -831,7 +833,7 @@
     <t>投与量</t>
   </si>
   <si>
-    <t>The value of the numerator.</t>
+    <t>分子の値。 / The value of the numerator.</t>
   </si>
   <si>
     <t>Ratio.numerator</t>
@@ -846,7 +848,7 @@
     <t>パッケージ量</t>
   </si>
   <si>
-    <t>The value of the denominator.</t>
+    <t>分母の値。 / The value of the denominator.</t>
   </si>
   <si>
     <t>&lt;valueQuantity xmlns="http://hl7.org/fhir"&gt;
@@ -1246,7 +1248,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="47.4921875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="79.203125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="50.48046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
